--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127704960</v>
+        <v>127703457</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>91330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>658648</v>
+        <v>658626</v>
       </c>
       <c r="R6" t="n">
-        <v>6545382</v>
+        <v>6545506</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703655</v>
+        <v>127704960</v>
       </c>
       <c r="B7" t="n">
-        <v>96050</v>
+        <v>79636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658626</v>
+        <v>658648</v>
       </c>
       <c r="R7" t="n">
-        <v>6545506</v>
+        <v>6545382</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,32 +1327,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703457</v>
+        <v>127703655</v>
       </c>
       <c r="B8" t="n">
-        <v>91330</v>
+        <v>96050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
         <v>6545506</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,6 +1539,1514 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127718004</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91314</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>658675</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6545335</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127717033</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>658631</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6545439</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127716896</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>658631</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6545439</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127716380</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92638</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>658634</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6545506</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127714653</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>658722</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6545342</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127714803</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96050</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>658722</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6545342</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127717213</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>658676</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6545418</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127718388</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>658617</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6545354</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127716390</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97328</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>658634</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6545506</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127718240</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96050</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>658617</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6545354</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127716784</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>658634</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6545469</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127714941</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92638</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>658758</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6545392</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127715387</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92622</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>788</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>658775</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6545390</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127718041</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57655</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>658639</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6545342</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127704702</v>
+        <v>127702868</v>
       </c>
       <c r="B3" t="n">
-        <v>91295</v>
+        <v>92640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658640</v>
+        <v>658777</v>
       </c>
       <c r="R3" t="n">
-        <v>6545424</v>
+        <v>6545487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127702868</v>
+        <v>127704702</v>
       </c>
       <c r="B4" t="n">
-        <v>92638</v>
+        <v>91297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658777</v>
+        <v>658640</v>
       </c>
       <c r="R4" t="n">
-        <v>6545487</v>
+        <v>6545424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>127703726</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,32 +1113,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127703457</v>
+        <v>127703655</v>
       </c>
       <c r="B6" t="n">
-        <v>91330</v>
+        <v>96052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
         <v>6545506</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1223,7 @@
         <v>127704960</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,32 +1327,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703655</v>
+        <v>127703457</v>
       </c>
       <c r="B8" t="n">
-        <v>96050</v>
+        <v>91332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
         <v>6545506</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>127702719</v>
       </c>
       <c r="B9" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127718004</v>
       </c>
       <c r="B10" t="n">
-        <v>91314</v>
+        <v>91316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127717033</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127716896</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,45 +1862,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127716380</v>
+        <v>127714653</v>
       </c>
       <c r="B13" t="n">
-        <v>92638</v>
+        <v>5177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658634</v>
+        <v>658722</v>
       </c>
       <c r="R13" t="n">
-        <v>6545506</v>
+        <v>6545342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,50 +1974,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127714653</v>
+        <v>127716380</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>92640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>658722</v>
+        <v>658634</v>
       </c>
       <c r="R14" t="n">
-        <v>6545342</v>
+        <v>6545506</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
         <v>127714803</v>
       </c>
       <c r="B15" t="n">
-        <v>96050</v>
+        <v>96052</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127717213</v>
+        <v>127718388</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>658676</v>
+        <v>658617</v>
       </c>
       <c r="R16" t="n">
-        <v>6545418</v>
+        <v>6545354</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,32 +2295,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127718388</v>
+        <v>127716390</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>97330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>221946</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>658617</v>
+        <v>658634</v>
       </c>
       <c r="R17" t="n">
-        <v>6545354</v>
+        <v>6545506</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127716390</v>
+        <v>127718240</v>
       </c>
       <c r="B18" t="n">
-        <v>97328</v>
+        <v>96052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,21 +2413,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>658634</v>
+        <v>658617</v>
       </c>
       <c r="R18" t="n">
-        <v>6545506</v>
+        <v>6545354</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,32 +2509,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127718240</v>
+        <v>127716784</v>
       </c>
       <c r="B19" t="n">
-        <v>96050</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,13 +2544,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>658617</v>
+        <v>658634</v>
       </c>
       <c r="R19" t="n">
-        <v>6545354</v>
+        <v>6545469</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,32 +2616,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127716784</v>
+        <v>127714941</v>
       </c>
       <c r="B20" t="n">
-        <v>98448</v>
+        <v>92640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>658634</v>
+        <v>658758</v>
       </c>
       <c r="R20" t="n">
-        <v>6545469</v>
+        <v>6545392</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127714941</v>
+        <v>127715387</v>
       </c>
       <c r="B21" t="n">
-        <v>92638</v>
+        <v>92624</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>658758</v>
+        <v>658775</v>
       </c>
       <c r="R21" t="n">
-        <v>6545392</v>
+        <v>6545390</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,48 +2830,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127715387</v>
+        <v>127718041</v>
       </c>
       <c r="B22" t="n">
-        <v>92622</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>788</v>
+        <v>102977</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>658775</v>
+        <v>658639</v>
       </c>
       <c r="R22" t="n">
-        <v>6545390</v>
+        <v>6545342</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2900,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,38 +2942,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127718041</v>
+        <v>127718640</v>
       </c>
       <c r="B23" t="n">
-        <v>57655</v>
+        <v>56602</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102977</v>
+        <v>100041</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2977,13 +2982,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>658639</v>
+        <v>658648</v>
       </c>
       <c r="R23" t="n">
-        <v>6545342</v>
+        <v>6545261</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3012,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3027,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -1862,50 +1862,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127714653</v>
+        <v>127716380</v>
       </c>
       <c r="B13" t="n">
-        <v>5177</v>
+        <v>92640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>4368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658722</v>
+        <v>658634</v>
       </c>
       <c r="R13" t="n">
-        <v>6545342</v>
+        <v>6545506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,45 +1969,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127716380</v>
+        <v>127714653</v>
       </c>
       <c r="B14" t="n">
-        <v>92640</v>
+        <v>5177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>658634</v>
+        <v>658722</v>
       </c>
       <c r="R14" t="n">
-        <v>6545506</v>
+        <v>6545342</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -1113,32 +1113,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127703655</v>
+        <v>127703457</v>
       </c>
       <c r="B6" t="n">
-        <v>96052</v>
+        <v>91332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
         <v>6545506</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127704960</v>
+        <v>127703655</v>
       </c>
       <c r="B7" t="n">
-        <v>79638</v>
+        <v>96052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658648</v>
+        <v>658626</v>
       </c>
       <c r="R7" t="n">
-        <v>6545382</v>
+        <v>6545506</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703457</v>
+        <v>127704960</v>
       </c>
       <c r="B8" t="n">
-        <v>91332</v>
+        <v>79638</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>658626</v>
+        <v>658648</v>
       </c>
       <c r="R8" t="n">
-        <v>6545506</v>
+        <v>6545382</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127702868</v>
       </c>
       <c r="B3" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127704702</v>
       </c>
       <c r="B4" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1113,32 +1113,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127703457</v>
+        <v>127703655</v>
       </c>
       <c r="B6" t="n">
-        <v>91332</v>
+        <v>96058</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
         <v>6545506</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703655</v>
+        <v>127703457</v>
       </c>
       <c r="B7" t="n">
-        <v>96052</v>
+        <v>91338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
         <v>6545506</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,7 +1437,7 @@
         <v>127702719</v>
       </c>
       <c r="B9" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127718004</v>
       </c>
       <c r="B10" t="n">
-        <v>91316</v>
+        <v>91322</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127716896</v>
       </c>
       <c r="B12" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,45 +1862,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127716380</v>
+        <v>127714653</v>
       </c>
       <c r="B13" t="n">
-        <v>92640</v>
+        <v>5177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658634</v>
+        <v>658722</v>
       </c>
       <c r="R13" t="n">
-        <v>6545506</v>
+        <v>6545342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,50 +1974,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127714653</v>
+        <v>127716380</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>92646</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>658722</v>
+        <v>658634</v>
       </c>
       <c r="R14" t="n">
-        <v>6545342</v>
+        <v>6545506</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
         <v>127714803</v>
       </c>
       <c r="B15" t="n">
-        <v>96052</v>
+        <v>96058</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127716390</v>
       </c>
       <c r="B17" t="n">
-        <v>97330</v>
+        <v>97336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>127718240</v>
       </c>
       <c r="B18" t="n">
-        <v>96052</v>
+        <v>96058</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>127716784</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>127714941</v>
       </c>
       <c r="B20" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>127715387</v>
       </c>
       <c r="B21" t="n">
-        <v>92624</v>
+        <v>92630</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127702868</v>
+        <v>127704702</v>
       </c>
       <c r="B3" t="n">
-        <v>92646</v>
+        <v>91306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658777</v>
+        <v>658640</v>
       </c>
       <c r="R3" t="n">
-        <v>6545487</v>
+        <v>6545424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127704702</v>
+        <v>127702868</v>
       </c>
       <c r="B4" t="n">
-        <v>91303</v>
+        <v>92649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658640</v>
+        <v>658777</v>
       </c>
       <c r="R4" t="n">
-        <v>6545424</v>
+        <v>6545487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>127703726</v>
       </c>
       <c r="B5" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>127703655</v>
       </c>
       <c r="B6" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>127703457</v>
       </c>
       <c r="B7" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>127704960</v>
       </c>
       <c r="B8" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127702719</v>
       </c>
       <c r="B9" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127718004</v>
       </c>
       <c r="B10" t="n">
-        <v>91322</v>
+        <v>91325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127717033</v>
       </c>
       <c r="B11" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127716896</v>
       </c>
       <c r="B12" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,50 +1862,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127714653</v>
+        <v>127716380</v>
       </c>
       <c r="B13" t="n">
-        <v>5177</v>
+        <v>92649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>4368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658722</v>
+        <v>658634</v>
       </c>
       <c r="R13" t="n">
-        <v>6545342</v>
+        <v>6545506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,45 +1969,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127716380</v>
+        <v>127714653</v>
       </c>
       <c r="B14" t="n">
-        <v>92646</v>
+        <v>5177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>658634</v>
+        <v>658722</v>
       </c>
       <c r="R14" t="n">
-        <v>6545506</v>
+        <v>6545342</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
         <v>127714803</v>
       </c>
       <c r="B15" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127718388</v>
       </c>
       <c r="B16" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127716390</v>
       </c>
       <c r="B17" t="n">
-        <v>97336</v>
+        <v>97339</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>127718240</v>
       </c>
       <c r="B18" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>127716784</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>127714941</v>
       </c>
       <c r="B20" t="n">
-        <v>92646</v>
+        <v>92649</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>127715387</v>
       </c>
       <c r="B21" t="n">
-        <v>92630</v>
+        <v>92633</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>127718041</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>127718640</v>
       </c>
       <c r="B23" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127704702</v>
+        <v>127702868</v>
       </c>
       <c r="B3" t="n">
-        <v>91306</v>
+        <v>92657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658640</v>
+        <v>658777</v>
       </c>
       <c r="R3" t="n">
-        <v>6545424</v>
+        <v>6545487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127702868</v>
+        <v>127704702</v>
       </c>
       <c r="B4" t="n">
-        <v>92649</v>
+        <v>91314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658777</v>
+        <v>658640</v>
       </c>
       <c r="R4" t="n">
-        <v>6545487</v>
+        <v>6545424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>127703726</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>127703655</v>
       </c>
       <c r="B6" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703457</v>
+        <v>127704960</v>
       </c>
       <c r="B7" t="n">
-        <v>91341</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658626</v>
+        <v>658648</v>
       </c>
       <c r="R7" t="n">
-        <v>6545506</v>
+        <v>6545382</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127704960</v>
+        <v>127703457</v>
       </c>
       <c r="B8" t="n">
-        <v>79641</v>
+        <v>91349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>658648</v>
+        <v>658626</v>
       </c>
       <c r="R8" t="n">
-        <v>6545382</v>
+        <v>6545506</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>127702719</v>
       </c>
       <c r="B9" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127718004</v>
       </c>
       <c r="B10" t="n">
-        <v>91325</v>
+        <v>91333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127717033</v>
       </c>
       <c r="B11" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127716896</v>
       </c>
       <c r="B12" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127716380</v>
       </c>
       <c r="B13" t="n">
-        <v>92649</v>
+        <v>92657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>127714803</v>
       </c>
       <c r="B15" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127718388</v>
       </c>
       <c r="B16" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127716390</v>
       </c>
       <c r="B17" t="n">
-        <v>97339</v>
+        <v>97347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>127718240</v>
       </c>
       <c r="B18" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>127716784</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>127714941</v>
       </c>
       <c r="B20" t="n">
-        <v>92649</v>
+        <v>92657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>127715387</v>
       </c>
       <c r="B21" t="n">
-        <v>92633</v>
+        <v>92641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>127718041</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>127718640</v>
       </c>
       <c r="B23" t="n">
-        <v>56605</v>
+        <v>56611</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127702868</v>
       </c>
       <c r="B3" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127704702</v>
       </c>
       <c r="B4" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>127703655</v>
       </c>
       <c r="B6" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>127703457</v>
       </c>
       <c r="B8" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127702719</v>
       </c>
       <c r="B9" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127718004</v>
       </c>
       <c r="B10" t="n">
-        <v>91333</v>
+        <v>91334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127716896</v>
       </c>
       <c r="B12" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,45 +1862,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127716380</v>
+        <v>127714653</v>
       </c>
       <c r="B13" t="n">
-        <v>92657</v>
+        <v>5177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658634</v>
+        <v>658722</v>
       </c>
       <c r="R13" t="n">
-        <v>6545506</v>
+        <v>6545342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,50 +1974,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127714653</v>
+        <v>127716380</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>92658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>658722</v>
+        <v>658634</v>
       </c>
       <c r="R14" t="n">
-        <v>6545342</v>
+        <v>6545506</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
         <v>127714803</v>
       </c>
       <c r="B15" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127716390</v>
       </c>
       <c r="B17" t="n">
-        <v>97347</v>
+        <v>97348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>127718240</v>
       </c>
       <c r="B18" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>127716784</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>127714941</v>
       </c>
       <c r="B20" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>127715387</v>
       </c>
       <c r="B21" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127704960</v>
+        <v>127703457</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658648</v>
+        <v>658626</v>
       </c>
       <c r="R7" t="n">
-        <v>6545382</v>
+        <v>6545506</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703457</v>
+        <v>127704960</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>79647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>658626</v>
+        <v>658648</v>
       </c>
       <c r="R8" t="n">
-        <v>6545506</v>
+        <v>6545382</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1862,50 +1862,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127714653</v>
+        <v>127716380</v>
       </c>
       <c r="B13" t="n">
-        <v>5177</v>
+        <v>92658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>4368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658722</v>
+        <v>658634</v>
       </c>
       <c r="R13" t="n">
-        <v>6545342</v>
+        <v>6545506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,45 +1969,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127716380</v>
+        <v>127714653</v>
       </c>
       <c r="B14" t="n">
-        <v>92658</v>
+        <v>5177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>658634</v>
+        <v>658722</v>
       </c>
       <c r="R14" t="n">
-        <v>6545506</v>
+        <v>6545342</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127702868</v>
+        <v>127704702</v>
       </c>
       <c r="B3" t="n">
-        <v>92658</v>
+        <v>91316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658777</v>
+        <v>658640</v>
       </c>
       <c r="R3" t="n">
-        <v>6545487</v>
+        <v>6545424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127704702</v>
+        <v>127702868</v>
       </c>
       <c r="B4" t="n">
-        <v>91315</v>
+        <v>92659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658640</v>
+        <v>658777</v>
       </c>
       <c r="R4" t="n">
-        <v>6545424</v>
+        <v>6545487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1116,7 +1116,7 @@
         <v>127703655</v>
       </c>
       <c r="B6" t="n">
-        <v>96070</v>
+        <v>96071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>127703457</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127702719</v>
       </c>
       <c r="B9" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127718004</v>
       </c>
       <c r="B10" t="n">
-        <v>91334</v>
+        <v>91335</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127716896</v>
       </c>
       <c r="B12" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127716380</v>
       </c>
       <c r="B13" t="n">
-        <v>92658</v>
+        <v>92659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>127714803</v>
       </c>
       <c r="B15" t="n">
-        <v>96070</v>
+        <v>96071</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127716390</v>
       </c>
       <c r="B17" t="n">
-        <v>97348</v>
+        <v>97349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>127718240</v>
       </c>
       <c r="B18" t="n">
-        <v>96070</v>
+        <v>96071</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>127716784</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>127714941</v>
       </c>
       <c r="B20" t="n">
-        <v>92658</v>
+        <v>92659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>127715387</v>
       </c>
       <c r="B21" t="n">
-        <v>92642</v>
+        <v>92643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127704702</v>
       </c>
       <c r="B3" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127702868</v>
       </c>
       <c r="B4" t="n">
-        <v>92659</v>
+        <v>92660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>127703655</v>
       </c>
       <c r="B6" t="n">
-        <v>96071</v>
+        <v>96072</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>127703457</v>
       </c>
       <c r="B7" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127702719</v>
       </c>
       <c r="B9" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127718004</v>
       </c>
       <c r="B10" t="n">
-        <v>91335</v>
+        <v>91336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127716896</v>
       </c>
       <c r="B12" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127716380</v>
       </c>
       <c r="B13" t="n">
-        <v>92659</v>
+        <v>92660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>127714803</v>
       </c>
       <c r="B15" t="n">
-        <v>96071</v>
+        <v>96072</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127716390</v>
       </c>
       <c r="B17" t="n">
-        <v>97349</v>
+        <v>97350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>127718240</v>
       </c>
       <c r="B18" t="n">
-        <v>96071</v>
+        <v>96072</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>127716784</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>127714941</v>
       </c>
       <c r="B20" t="n">
-        <v>92659</v>
+        <v>92660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>127715387</v>
       </c>
       <c r="B21" t="n">
-        <v>92643</v>
+        <v>92644</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127704702</v>
+        <v>127702868</v>
       </c>
       <c r="B3" t="n">
-        <v>91317</v>
+        <v>92660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658640</v>
+        <v>658777</v>
       </c>
       <c r="R3" t="n">
-        <v>6545424</v>
+        <v>6545487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127702868</v>
+        <v>127704702</v>
       </c>
       <c r="B4" t="n">
-        <v>92660</v>
+        <v>91317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658777</v>
+        <v>658640</v>
       </c>
       <c r="R4" t="n">
-        <v>6545487</v>
+        <v>6545424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1113,32 +1113,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127703655</v>
+        <v>127703457</v>
       </c>
       <c r="B6" t="n">
-        <v>96072</v>
+        <v>91352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
         <v>6545506</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703457</v>
+        <v>127703655</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>96072</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
         <v>6545506</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703655</v>
+        <v>127704960</v>
       </c>
       <c r="B7" t="n">
-        <v>96072</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658626</v>
+        <v>658648</v>
       </c>
       <c r="R7" t="n">
-        <v>6545506</v>
+        <v>6545382</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,32 +1327,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127704960</v>
+        <v>127703655</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>96072</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>658648</v>
+        <v>658626</v>
       </c>
       <c r="R8" t="n">
-        <v>6545382</v>
+        <v>6545506</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127704960</v>
+        <v>127703655</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>96072</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658648</v>
+        <v>658626</v>
       </c>
       <c r="R7" t="n">
-        <v>6545382</v>
+        <v>6545506</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,32 +1327,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703655</v>
+        <v>127704960</v>
       </c>
       <c r="B8" t="n">
-        <v>96072</v>
+        <v>79647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>658626</v>
+        <v>658648</v>
       </c>
       <c r="R8" t="n">
-        <v>6545506</v>
+        <v>6545382</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127702868</v>
+        <v>127704702</v>
       </c>
       <c r="B3" t="n">
-        <v>92660</v>
+        <v>91325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658777</v>
+        <v>658640</v>
       </c>
       <c r="R3" t="n">
-        <v>6545487</v>
+        <v>6545424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127704702</v>
+        <v>127702868</v>
       </c>
       <c r="B4" t="n">
-        <v>91317</v>
+        <v>92668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658640</v>
+        <v>658777</v>
       </c>
       <c r="R4" t="n">
-        <v>6545424</v>
+        <v>6545487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>127703726</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127703457</v>
+        <v>127704960</v>
       </c>
       <c r="B6" t="n">
-        <v>91352</v>
+        <v>79650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>658626</v>
+        <v>658648</v>
       </c>
       <c r="R6" t="n">
-        <v>6545506</v>
+        <v>6545382</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127704960</v>
+        <v>127703655</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>96080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658648</v>
+        <v>658626</v>
       </c>
       <c r="R7" t="n">
-        <v>6545382</v>
+        <v>6545506</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,32 +1327,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703655</v>
+        <v>127703457</v>
       </c>
       <c r="B8" t="n">
-        <v>96072</v>
+        <v>91360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
         <v>6545506</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>127702719</v>
       </c>
       <c r="B9" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127718004</v>
       </c>
       <c r="B10" t="n">
-        <v>91336</v>
+        <v>91344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127717033</v>
       </c>
       <c r="B11" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127716896</v>
       </c>
       <c r="B12" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127716380</v>
       </c>
       <c r="B13" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>127714803</v>
       </c>
       <c r="B15" t="n">
-        <v>96072</v>
+        <v>96080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127718388</v>
       </c>
       <c r="B16" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127716390</v>
       </c>
       <c r="B17" t="n">
-        <v>97350</v>
+        <v>97358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>127718240</v>
       </c>
       <c r="B18" t="n">
-        <v>96072</v>
+        <v>96080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>127716784</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>127714941</v>
       </c>
       <c r="B20" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>127715387</v>
       </c>
       <c r="B21" t="n">
-        <v>92644</v>
+        <v>92652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>127718041</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57667</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127704702</v>
       </c>
       <c r="B3" t="n">
-        <v>91325</v>
+        <v>91336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>127702868</v>
       </c>
       <c r="B4" t="n">
-        <v>92668</v>
+        <v>92679</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127703726</v>
       </c>
       <c r="B5" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,32 +1113,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127704960</v>
+        <v>127703655</v>
       </c>
       <c r="B6" t="n">
-        <v>79650</v>
+        <v>96092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>658648</v>
+        <v>658626</v>
       </c>
       <c r="R6" t="n">
-        <v>6545382</v>
+        <v>6545506</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703655</v>
+        <v>127704960</v>
       </c>
       <c r="B7" t="n">
-        <v>96080</v>
+        <v>79661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658626</v>
+        <v>658648</v>
       </c>
       <c r="R7" t="n">
-        <v>6545506</v>
+        <v>6545382</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,7 +1330,7 @@
         <v>127703457</v>
       </c>
       <c r="B8" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127702719</v>
       </c>
       <c r="B9" t="n">
-        <v>97355</v>
+        <v>97367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127718004</v>
       </c>
       <c r="B10" t="n">
-        <v>91344</v>
+        <v>91355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127717033</v>
       </c>
       <c r="B11" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127716896</v>
       </c>
       <c r="B12" t="n">
-        <v>91380</v>
+        <v>91391</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,45 +1862,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127716380</v>
+        <v>127714653</v>
       </c>
       <c r="B13" t="n">
-        <v>92668</v>
+        <v>5177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658634</v>
+        <v>658722</v>
       </c>
       <c r="R13" t="n">
-        <v>6545506</v>
+        <v>6545342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,50 +1974,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127714653</v>
+        <v>127716380</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>92679</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>658722</v>
+        <v>658634</v>
       </c>
       <c r="R14" t="n">
-        <v>6545342</v>
+        <v>6545506</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
         <v>127714803</v>
       </c>
       <c r="B15" t="n">
-        <v>96080</v>
+        <v>96092</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127718388</v>
       </c>
       <c r="B16" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127716390</v>
       </c>
       <c r="B17" t="n">
-        <v>97358</v>
+        <v>97370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>127718240</v>
       </c>
       <c r="B18" t="n">
-        <v>96080</v>
+        <v>96092</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>127716784</v>
       </c>
       <c r="B19" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>127714941</v>
       </c>
       <c r="B20" t="n">
-        <v>92668</v>
+        <v>92679</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>127715387</v>
       </c>
       <c r="B21" t="n">
-        <v>92652</v>
+        <v>92663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>127718041</v>
       </c>
       <c r="B22" t="n">
-        <v>57667</v>
+        <v>57678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>127718640</v>
       </c>
       <c r="B23" t="n">
-        <v>56611</v>
+        <v>56623</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -2945,7 +2945,7 @@
         <v>127718640</v>
       </c>
       <c r="B23" t="n">
-        <v>56623</v>
+        <v>56627</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -2945,7 +2945,7 @@
         <v>127718640</v>
       </c>
       <c r="B23" t="n">
-        <v>56627</v>
+        <v>56654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -2945,7 +2945,7 @@
         <v>127718640</v>
       </c>
       <c r="B23" t="n">
-        <v>56654</v>
+        <v>56657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -2945,7 +2945,7 @@
         <v>127718640</v>
       </c>
       <c r="B23" t="n">
-        <v>56657</v>
+        <v>56660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -2945,7 +2945,7 @@
         <v>127718640</v>
       </c>
       <c r="B23" t="n">
-        <v>56660</v>
+        <v>56662</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3052,6 +3052,122 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129842005</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Eriksberg (*knärot* /stjälk/), Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>658635</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6545468</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>AB-Nyn-0116</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Eriksberg, Obskoord: 6545821/1612466/8 m ().</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129842005</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129842005</v>
       </c>
       <c r="B24" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129842005</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129842005</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129842005</v>
       </c>
       <c r="B24" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129842005</v>
       </c>
       <c r="B24" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129842005</v>
       </c>
       <c r="B24" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129842005</v>
       </c>
       <c r="B24" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2025 artfynd.xlsx
+++ b/artfynd/A 35557-2025 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129842005</v>
       </c>
       <c r="B24" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
